--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1536583069740586</v>
+        <v>0.1536583069740585</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03038827855213699</v>
+        <v>0.03038827855213695</v>
       </c>
       <c r="I2" t="n">
-        <v>0.292115036150392</v>
+        <v>0.2921150361503924</v>
       </c>
     </row>
     <row r="3">
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.09116059753960712</v>
+        <v>0.09116059753960701</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04287867595649834</v>
+        <v>0.04287867595649825</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733025813584513</v>
+        <v>0.1733025813584514</v>
       </c>
     </row>
     <row r="4">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.08216296529744091</v>
+        <v>0.08216296529744077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03698891674220324</v>
+        <v>0.03698891674220323</v>
       </c>
       <c r="I4" t="n">
         <v>0.1561974620879907</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.07488760483557048</v>
+        <v>0.0748876048355704</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0315725034166981</v>
+        <v>0.03157250341669809</v>
       </c>
       <c r="I5" t="n">
         <v>0.1423665002208578</v>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.05383327097702401</v>
+        <v>0.05383327097702387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02790831491678825</v>
+        <v>0.02790831491678831</v>
       </c>
       <c r="I6" t="n">
-        <v>0.10234075987966</v>
+        <v>0.1023407598796599</v>
       </c>
     </row>
     <row r="7">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.04281159211820092</v>
+        <v>0.04281159211820077</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02623400359195475</v>
+        <v>0.0262340035919547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0813877884348642</v>
+        <v>0.08138778843486405</v>
       </c>
     </row>
     <row r="8">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.02124909736084166</v>
+        <v>0.0212490973608415</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00812266722240295</v>
+        <v>0.008122667222402962</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04039599918781736</v>
+        <v>0.04039599918781712</v>
       </c>
     </row>
     <row r="9">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.006256413101678815</v>
+        <v>0.006256413101678704</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00705397073405427</v>
+        <v>0.007053970734054277</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01189387267996671</v>
+        <v>0.01189387267996652</v>
       </c>
     </row>
   </sheetData>

--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,7 +654,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.204329139603543</v>
+        <v>0.3106120099366012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.204329139603543</v>
+        <v>0.3106120099366012</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1689632065821456</v>
+        <v>0.1049758169925582</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1689632065821456</v>
+        <v>0.1049758169925582</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.1618267404670949</v>
+        <v>0.06752460075490486</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1618267404670949</v>
+        <v>0.06752460075490486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.1537094963920569</v>
+        <v>0.04934190146444293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1537094963920569</v>
+        <v>0.04934190146444293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.1449909557258946</v>
+        <v>0.04764537856767835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1449909557258946</v>
+        <v>0.04764537856767835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.1265069153654246</v>
+        <v>0.04482147814045997</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1265069153654246</v>
+        <v>0.04482147814045997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.02007632898149883</v>
+        <v>0.04006902093562956</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02007632898149883</v>
+        <v>0.04006902093562956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -919,24 +919,708 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03542869559244693</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03542869559244693</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03490641171033726</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03490641171033726</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.03452346191986672</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03452346191986672</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.03316245725025326</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.03316245725025326</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.02467920781168377</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02467920781168377</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.02104081688669567</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02104081688669567</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01900842550716646</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.01900842550716646</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01711998658266793</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01711998658266793</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.01500969863757983</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.01500969863757983</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.01495346917951096</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01495346917951096</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01394269970336033</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01394269970336033</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.01114598034217666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.01114598034217666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.01097914895966731</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.01097914895966731</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0109671634718552</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0109671634718552</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.009722272491172147</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.009722272491172147</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.00936875837619079</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00936875837619079</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.008361343108824578</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.008361343108824578</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.007564319389440822</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.007564319389440822</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>lime_milk_baume</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>lime_milk_baume</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01959721688234163</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01959721688234163</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.001826183884130568</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.001826183884130568</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.001299292402697787</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.001299292402697787</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +1634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,7 +1687,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1016,12 +1700,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1030,19 +1714,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1536583069740585</v>
+        <v>0.281308596334786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03038827855213695</v>
+        <v>0.06393941953858416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2921150361503924</v>
+        <v>0.3234507010306096</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1055,12 +1739,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1069,19 +1753,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.09116059753960701</v>
+        <v>0.1988007498424338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04287867595649825</v>
+        <v>0.03954638804507479</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733025813584514</v>
+        <v>0.2285825699596461</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1094,12 +1778,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1108,19 +1792,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.08216296529744077</v>
+        <v>0.1196062299300397</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03698891674220323</v>
+        <v>0.02754612041108619</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1561974620879907</v>
+        <v>0.1375241262533565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1133,12 +1817,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1147,19 +1831,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.0748876048355704</v>
+        <v>0.03317804298573546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03157250341669809</v>
+        <v>0.01285741329445621</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1423665002208578</v>
+        <v>0.03814835878597999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1172,12 +1856,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1186,19 +1870,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.05383327097702387</v>
+        <v>0.03297436127279139</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02790831491678831</v>
+        <v>0.008647570417966254</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1023407598796599</v>
+        <v>0.03791416404860884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1211,12 +1895,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1225,19 +1909,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.04281159211820077</v>
+        <v>0.03034446087549219</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0262340035919547</v>
+        <v>0.01349825339562126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08138778843486405</v>
+        <v>0.03489028515464587</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1250,12 +1934,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1264,19 +1948,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.0212490973608415</v>
+        <v>0.02849101557612364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008122667222402962</v>
+        <v>0.008793782713450249</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04039599918781712</v>
+        <v>0.03275918006502685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1289,27 +1973,768 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02540640511142909</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01135305355800244</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02921247217834564</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.02227829568191981</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01091250670730217</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02561574886075779</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01996873296036933</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.007271868512932694</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02296019659149608</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01535180002081509</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.00744491136403479</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01765161300973844</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01186787086258106</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.009171741839974932</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01364576554096548</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01075337450634401</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01143073777842844</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01236430940198592</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.006256413101678704</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.007053970734054277</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01189387267996652</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.009876169769574172</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.008800993379959342</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01135569291904735</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.007567705338824315</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.009325165367417248</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.008701403472657137</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.003984012051805208</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.001973392670282836</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.004580846472026005</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.002697932674882031</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.001481112223488514</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.003102102909025361</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.002533154425005335</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.001290413448884202</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.002912639660722118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.001939565070978677</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.001236124225923622</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.002230126238858062</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.001929276224087129</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.001230556974841218</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.002218296046737281</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.001873003697391751</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.001767754243591144</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.002153593480070167</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001729382646128275</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.005693074603900009</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.001988456934940778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001486605820025067</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.004669279653653466</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.001709310347811195</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001418383068929785</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.001915009924785807</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.001630867324897867</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001372039600365371</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.003989471644513134</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.001577581262578214</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0002371591613371748</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0004717516603342512</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0002726873547051109</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.0007365622339145506</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.002822028404289039</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0008469046947602035</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,7 +2796,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1384,12 +2809,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1398,16 +2823,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5770975514410538</v>
+        <v>0.1469366142321696</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2421652909166376</v>
+        <v>0.3221008627014287</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1434,16 +2859,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5630007396052262</v>
+        <v>0.0617404232201974</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2362498983964374</v>
+        <v>0.1353416484155181</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1456,12 +2881,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1470,16 +2895,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.3247026153755668</v>
+        <v>0.04426903143771559</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1362537462123488</v>
+        <v>0.09704247842892685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1492,12 +2917,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1506,16 +2931,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.3096483086002679</v>
+        <v>0.0220708426260788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.129936563665507</v>
+        <v>0.04838166094649968</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1528,12 +2953,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1542,16 +2967,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.2702867622367928</v>
+        <v>0.02136629287273234</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1134194249213941</v>
+        <v>0.04683721210674079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1564,12 +2989,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1578,16 +3003,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.2581000950960951</v>
+        <v>0.01803873214118227</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1083055792880832</v>
+        <v>0.03954284107522824</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1600,12 +3025,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1614,16 +3039,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04917452961969403</v>
+        <v>0.01801745794147925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02063492427113229</v>
+        <v>0.03949620574125492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1636,24 +3061,708 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01399464844901344</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03067777464579384</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01346336685550061</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02951314824888039</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01330782772885502</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02917218975369408</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01249691470318723</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0273945811807164</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01175554579830345</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02576942080056931</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01034233444542276</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02267150951194328</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.008180669429195377</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0179329072905924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.03106233658160693</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01303457232845961</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.006960330694267783</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01525779352563883</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.006487956803490367</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.01422229914915466</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005464789628895069</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01197940665195721</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.004042426073329889</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.00886143275064819</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.002919976447496348</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.006400902441649649</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.002725162315299852</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.005973848909929009</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.002655384206342384</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.005820887789854729</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.002433095230060372</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.005333606444741378</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001842179787109819</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.004038256235723839</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001829522092787521</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.004010509208324792</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001472614407866125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.003228129174466748</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0009419858761366918</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.002064934359224956</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0004258698471309827</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.000933552510898833</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +3776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,56 +3789,189 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
         </is>
       </c>
     </row>

--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,7 +654,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.3106120099366012</v>
+        <v>0.1297872949151567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3106120099366012</v>
+        <v>0.1297872949151567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1049758169925582</v>
+        <v>0.1179640167580736</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1049758169925582</v>
+        <v>0.1179640167580736</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.06752460075490486</v>
+        <v>0.08372680232724868</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06752460075490486</v>
+        <v>0.08372680232724868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.04934190146444293</v>
+        <v>0.07369204801215536</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04934190146444293</v>
+        <v>0.07369204801215536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.04764537856767835</v>
+        <v>0.07081170122822732</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04764537856767835</v>
+        <v>0.07081170122822732</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.04482147814045997</v>
+        <v>0.06553695878618569</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04482147814045997</v>
+        <v>0.06553695878618569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04006902093562956</v>
+        <v>0.05797102672814126</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04006902093562956</v>
+        <v>0.05797102672814126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.03542869559244693</v>
+        <v>0.05125508080105356</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03542869559244693</v>
+        <v>0.05125508080105356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.03490641171033726</v>
+        <v>0.02989599839874472</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03490641171033726</v>
+        <v>0.02989599839874472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.03452346191986672</v>
+        <v>0.02984744466613669</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03452346191986672</v>
+        <v>0.02984744466613669</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.03316245725025326</v>
+        <v>0.02624735115605701</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03316245725025326</v>
+        <v>0.02624735115605701</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.02467920781168377</v>
+        <v>0.02562398123516254</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02467920781168377</v>
+        <v>0.02562398123516254</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.02104081688669567</v>
+        <v>0.02525294320172626</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02104081688669567</v>
+        <v>0.02525294320172626</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.01900842550716646</v>
+        <v>0.02411922866950809</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01900842550716646</v>
+        <v>0.02411922866950809</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.01711998658266793</v>
+        <v>0.02046567651770588</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01711998658266793</v>
+        <v>0.02046567651770588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.01500969863757983</v>
+        <v>0.01953350666529102</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01500969863757983</v>
+        <v>0.01953350666529102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.01495346917951096</v>
+        <v>0.0169581541977361</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01495346917951096</v>
+        <v>0.0169581541977361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.01394269970336033</v>
+        <v>0.01689911034154988</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01394269970336033</v>
+        <v>0.01689911034154988</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.01114598034217666</v>
+        <v>0.01629283238394655</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01114598034217666</v>
+        <v>0.01629283238394655</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.01097914895966731</v>
+        <v>0.01560403697523521</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01097914895966731</v>
+        <v>0.01560403697523521</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.0109671634718552</v>
+        <v>0.0149756938468358</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0109671634718552</v>
+        <v>0.0149756938468358</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1437,16 +1437,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.009722272491172147</v>
+        <v>0.01230180684479502</v>
       </c>
       <c r="H23" t="n">
-        <v>0.009722272491172147</v>
+        <v>0.01230180684479502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1473,16 +1473,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.00936875837619079</v>
+        <v>0.0111333705819733</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00936875837619079</v>
+        <v>0.0111333705819733</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.008361343108824578</v>
+        <v>0.01100678424197596</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008361343108824578</v>
+        <v>0.01100678424197596</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.007564319389440822</v>
+        <v>0.01082468240389748</v>
       </c>
       <c r="H26" t="n">
-        <v>0.007564319389440822</v>
+        <v>0.01082468240389748</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.001826183884130568</v>
+        <v>0.01037312331709658</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001826183884130568</v>
+        <v>0.01037312331709658</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1603,24 +1603,60 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.01011448707719072</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01011448707719072</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Random Forest Importance</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>boiler_hardness</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>boiler_hardness</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0.001299292402697787</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.001299292402697787</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.00178485772119311</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00178485772119311</v>
       </c>
     </row>
   </sheetData>
@@ -1634,7 +1670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,7 +1723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1700,12 +1736,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1714,19 +1750,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.281308596334786</v>
+        <v>0.1208222616241149</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06393941953858416</v>
+        <v>0.04624424822799004</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3234507010306096</v>
+        <v>0.192660534689863</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1739,12 +1775,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1753,19 +1789,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1988007498424338</v>
+        <v>0.09493913788330618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03954638804507479</v>
+        <v>0.02091437723053542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2285825699596461</v>
+        <v>0.1513878719179818</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1792,19 +1828,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.1196062299300397</v>
+        <v>0.0724475560067533</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02754612041108619</v>
+        <v>0.01979407399214912</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1375241262533565</v>
+        <v>0.1155232875929633</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1817,12 +1853,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1831,19 +1867,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.03317804298573546</v>
+        <v>0.0544978636267555</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01285741329445621</v>
+        <v>0.02412711720990972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03814835878597999</v>
+        <v>0.08690110087866731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1856,12 +1892,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1870,19 +1906,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.03297436127279139</v>
+        <v>0.04893802609278455</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008647570417966254</v>
+        <v>0.01125272720760447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03791416404860884</v>
+        <v>0.07803550560106809</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1895,12 +1931,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1909,19 +1945,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.03034446087549219</v>
+        <v>0.0445298630863198</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01349825339562126</v>
+        <v>0.01363313217761007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03489028515464587</v>
+        <v>0.071006345325392</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1934,12 +1970,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1948,19 +1984,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.02849101557612364</v>
+        <v>0.04104928587923653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008793782713450249</v>
+        <v>0.007389694768749089</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03275918006502685</v>
+        <v>0.06545629306902724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1973,12 +2009,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1987,19 +2023,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.02540640511142909</v>
+        <v>0.0326309145989926</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01135305355800244</v>
+        <v>0.008536093787784145</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02921247217834564</v>
+        <v>0.05203254242682052</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2026,19 +2062,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.02227829568191981</v>
+        <v>0.01859684813391253</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01091250670730217</v>
+        <v>0.01117624141826805</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02561574886075779</v>
+        <v>0.02965412711915881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2051,12 +2087,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2065,19 +2101,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.01996873296036933</v>
+        <v>0.01290971951045673</v>
       </c>
       <c r="H11" t="n">
-        <v>0.007271868512932694</v>
+        <v>0.004259142807845186</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02296019659149608</v>
+        <v>0.02058555625550656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2104,19 +2140,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.01535180002081509</v>
+        <v>0.01155749953883107</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00744491136403479</v>
+        <v>0.004801947076014734</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01765161300973844</v>
+        <v>0.01842933587649891</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2129,12 +2165,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2143,19 +2179,19 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.01186787086258106</v>
+        <v>0.01023934088509111</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009171741839974932</v>
+        <v>0.005373597862283417</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01364576554096548</v>
+        <v>0.01632742892970059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2168,12 +2204,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2182,19 +2218,19 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.01075337450634401</v>
+        <v>0.01017034629079663</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01143073777842844</v>
+        <v>0.003760355901858563</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01236430940198592</v>
+        <v>0.01621741165930022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2207,12 +2243,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2221,19 +2257,19 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.009876169769574172</v>
+        <v>0.007556786977392827</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008800993379959342</v>
+        <v>0.003631487163269581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01135569291904735</v>
+        <v>0.0120498871650927</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2246,12 +2282,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2260,19 +2296,19 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.007567705338824315</v>
+        <v>0.006568436404767208</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009325165367417248</v>
+        <v>0.002196072363767359</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008701403472657137</v>
+        <v>0.01047388496795225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2285,12 +2321,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2299,19 +2335,19 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.003984012051805208</v>
+        <v>0.00593297067347579</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001973392670282836</v>
+        <v>0.00123612970626391</v>
       </c>
       <c r="I17" t="n">
-        <v>0.004580846472026005</v>
+        <v>0.0094605852173767</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2324,12 +2360,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2338,19 +2374,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.002697932674882031</v>
+        <v>0.005420439767237373</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001481112223488514</v>
+        <v>0.001535155879387675</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003102102909025361</v>
+        <v>0.008643314648909994</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2363,12 +2399,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2377,19 +2413,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.002533154425005335</v>
+        <v>0.005314336291431809</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001290413448884202</v>
+        <v>0.002030618974674196</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002912639660722118</v>
+        <v>0.008474124368026584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2402,12 +2438,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2416,19 +2452,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.001939565070978677</v>
+        <v>0.003514350607873695</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001236124225923622</v>
+        <v>0.006110902823824402</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002230126238858062</v>
+        <v>0.005603906582273851</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,12 +2477,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2455,19 +2491,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.001929276224087129</v>
+        <v>0.0034441481240021</v>
       </c>
       <c r="H21" t="n">
-        <v>0.001230556974841218</v>
+        <v>0.00237696540288218</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002218296046737281</v>
+        <v>0.005491963237583484</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2480,12 +2516,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2494,19 +2530,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.001873003697391751</v>
+        <v>0.002929585104837673</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001767754243591144</v>
+        <v>0.001094060827094026</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002153593480070167</v>
+        <v>0.004671452306309358</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2519,12 +2555,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2533,19 +2569,19 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.001729382646128275</v>
+        <v>0.0008430978935825229</v>
       </c>
       <c r="H23" t="n">
-        <v>0.005693074603900009</v>
+        <v>0.001967829439132348</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001988456934940778</v>
+        <v>0.001344385453393022</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2558,12 +2594,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2572,19 +2608,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.001486605820025067</v>
+        <v>0.0002509742748877164</v>
       </c>
       <c r="H24" t="n">
-        <v>0.004669279653653466</v>
+        <v>0.001396474164201583</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001709310347811195</v>
+        <v>0.0004001980872009875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2597,12 +2633,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2611,19 +2647,19 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.001418383068929785</v>
+        <v>-3.471688116681859e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001915009924785807</v>
+        <v>0.0005124481320309013</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001630867324897867</v>
+        <v>5.535877907311685e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2636,12 +2672,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2650,19 +2686,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.001372039600365371</v>
+        <v>-0.0006610909967943335</v>
       </c>
       <c r="H26" t="n">
-        <v>0.003989471644513134</v>
+        <v>0.002634289943162154</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001577581262578214</v>
+        <v>0.001054161238243447</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2675,12 +2711,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2689,19 +2725,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.0002371591613371748</v>
+        <v>-0.001380781816066512</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0004717516603342512</v>
+        <v>0.002252328579339999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0002726873547051109</v>
+        <v>0.00220176447119509</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2714,12 +2750,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2728,13 +2764,52 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.0007365622339145506</v>
+        <v>-0.004036032184131799</v>
       </c>
       <c r="H28" t="n">
-        <v>0.002822028404289039</v>
+        <v>0.003272425233031639</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0008469046947602035</v>
+        <v>0.006435768608929348</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Permutation Importance</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.005908712413299766</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.003273920317167908</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0094219035264918</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2796,7 +2871,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2809,12 +2884,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2823,16 +2898,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1469366142321696</v>
+        <v>0.5331940672099847</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3221008627014287</v>
+        <v>0.1882448091871627</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2859,16 +2934,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.0617404232201974</v>
+        <v>0.5317596057027448</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1353416484155181</v>
+        <v>0.1877383708201162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2881,12 +2956,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2895,16 +2970,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.04426903143771559</v>
+        <v>0.3101229488715436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09704247842892685</v>
+        <v>0.1094892815300078</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2931,16 +3006,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.0220708426260788</v>
+        <v>0.150034987623731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04838166094649968</v>
+        <v>0.05297003352721975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2953,12 +3028,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2967,16 +3042,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.02136629287273234</v>
+        <v>0.136893280236189</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04683721210674079</v>
+        <v>0.04833033786723955</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2989,12 +3064,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3003,16 +3078,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.01803873214118227</v>
+        <v>0.127022464124849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03954284107522824</v>
+        <v>0.04484543432147484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3039,16 +3114,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.01801745794147925</v>
+        <v>0.1250752191451133</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03949620574125492</v>
+        <v>0.04415795713034801</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3061,12 +3136,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3075,16 +3150,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.01399464844901344</v>
+        <v>0.1033111363986668</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03067777464579384</v>
+        <v>0.03647412143957138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3097,12 +3172,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3111,16 +3186,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.01346336685550061</v>
+        <v>0.08147973689608093</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02951314824888039</v>
+        <v>0.02876651948676399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3133,12 +3208,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3147,16 +3222,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.01330782772885502</v>
+        <v>0.07053537520787416</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02917218975369408</v>
+        <v>0.0249025993789275</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3169,12 +3244,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3183,16 +3258,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.01249691470318723</v>
+        <v>0.06996642889195488</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0273945811807164</v>
+        <v>0.02470173219516759</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3205,12 +3280,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3219,16 +3294,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.01175554579830345</v>
+        <v>0.06641100418790037</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02576942080056931</v>
+        <v>0.02344648521071365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3241,12 +3316,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3255,16 +3330,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.01034233444542276</v>
+        <v>0.05926428584548547</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02267150951194328</v>
+        <v>0.02092332767124226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3277,12 +3352,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3291,16 +3366,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.008180669429195377</v>
+        <v>0.05903958211308907</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0179329072905924</v>
+        <v>0.02084399574722078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3313,12 +3388,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3327,16 +3402,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.006960330694267783</v>
+        <v>0.05779571922305082</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01525779352563883</v>
+        <v>0.02040484845209901</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3349,12 +3424,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3363,16 +3438,16 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.006487956803490367</v>
+        <v>0.04574499966006754</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01422229914915466</v>
+        <v>0.01615032736079735</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3385,12 +3460,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3399,16 +3474,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.005464789628895069</v>
+        <v>0.04524119219295129</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01197940665195721</v>
+        <v>0.01597245752625356</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3421,12 +3496,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3435,16 +3510,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.004042426073329889</v>
+        <v>0.0356079322427973</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00886143275064819</v>
+        <v>0.01257142347001207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3457,12 +3532,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3471,16 +3546,16 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.002919976447496348</v>
+        <v>0.03245637190318106</v>
       </c>
       <c r="H20" t="n">
-        <v>0.006400902441649649</v>
+        <v>0.01145876128703387</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3493,12 +3568,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3507,16 +3582,16 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.002725162315299852</v>
+        <v>0.03125598070877662</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005973848909929009</v>
+        <v>0.01103496172654172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3529,12 +3604,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3543,16 +3618,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.002655384206342384</v>
+        <v>0.03053247130583358</v>
       </c>
       <c r="H22" t="n">
-        <v>0.005820887789854729</v>
+        <v>0.01077952585829434</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3565,12 +3640,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3579,16 +3654,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.002433095230060372</v>
+        <v>0.02985985069865335</v>
       </c>
       <c r="H23" t="n">
-        <v>0.005333606444741378</v>
+        <v>0.01054205634083227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3601,12 +3676,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3615,16 +3690,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.001842179787109819</v>
+        <v>0.02592690845307678</v>
       </c>
       <c r="H24" t="n">
-        <v>0.004038256235723839</v>
+        <v>0.00915352633254333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3637,12 +3712,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3651,16 +3726,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.001829522092787521</v>
+        <v>0.02470182689715563</v>
       </c>
       <c r="H25" t="n">
-        <v>0.004010509208324792</v>
+        <v>0.008721009810107481</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3673,12 +3748,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3687,16 +3762,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.001472614407866125</v>
+        <v>0.01583557178118171</v>
       </c>
       <c r="H26" t="n">
-        <v>0.003228129174466748</v>
+        <v>0.005590767736626358</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3709,12 +3784,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3723,16 +3798,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.0009419858761366918</v>
+        <v>0.01444026510879617</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002064934359224956</v>
+        <v>0.005098153031299285</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3745,12 +3820,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3759,10 +3834,46 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.0004258698471309827</v>
+        <v>0.01391099145843254</v>
       </c>
       <c r="H28" t="n">
-        <v>0.000933552510898833</v>
+        <v>0.004911292330013092</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>white_total_points</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SHAP Mean Absolute Value</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.005030100980635893</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.001775883224370265</v>
       </c>
     </row>
   </sheetData>
@@ -3776,7 +3887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3789,187 +3900,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>boiler_tds</t>
         </is>

--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1208222616241149</v>
+        <v>0.1208222616241151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04624424822799004</v>
+        <v>0.04624424822799005</v>
       </c>
       <c r="I2" t="n">
-        <v>0.192660534689863</v>
+        <v>0.192660534689862</v>
       </c>
     </row>
     <row r="3">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.09493913788330618</v>
+        <v>0.09493913788330646</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02091437723053542</v>
+        <v>0.02091437723053539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1513878719179818</v>
+        <v>0.1513878719179812</v>
       </c>
     </row>
     <row r="4">
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.0724475560067533</v>
+        <v>0.07244755600675354</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01979407399214912</v>
+        <v>0.01979407399214914</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1155232875929633</v>
+        <v>0.1155232875929629</v>
       </c>
     </row>
     <row r="5">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.0544978636267555</v>
+        <v>0.05449786362675575</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02412711720990972</v>
+        <v>0.02412711720990969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08690110087866731</v>
+        <v>0.08690110087866716</v>
       </c>
     </row>
     <row r="6">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.04893802609278455</v>
+        <v>0.0489380260927848</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01125272720760447</v>
+        <v>0.01125272720760455</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07803550560106809</v>
+        <v>0.07803550560106799</v>
       </c>
     </row>
     <row r="7">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.0445298630863198</v>
+        <v>0.04452986308632003</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01363313217761007</v>
+        <v>0.01363313217761005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.071006345325392</v>
+        <v>0.07100634532539191</v>
       </c>
     </row>
     <row r="8">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04104928587923653</v>
+        <v>0.04104928587923673</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007389694768749089</v>
+        <v>0.007389694768749083</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06545629306902724</v>
+        <v>0.06545629306902713</v>
       </c>
     </row>
     <row r="9">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.0326309145989926</v>
+        <v>0.03263091459899287</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008536093787784145</v>
+        <v>0.008536093787784131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05203254242682052</v>
+        <v>0.0520325424268206</v>
       </c>
     </row>
     <row r="10">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.01859684813391253</v>
+        <v>0.0185968481339127</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01117624141826805</v>
+        <v>0.01117624141826799</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02965412711915881</v>
+        <v>0.0296541271191589</v>
       </c>
     </row>
     <row r="11">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.01290971951045673</v>
+        <v>0.01290971951045696</v>
       </c>
       <c r="H11" t="n">
-        <v>0.004259142807845186</v>
+        <v>0.004259142807845136</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02058555625550656</v>
+        <v>0.0205855562555068</v>
       </c>
     </row>
     <row r="12">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.01155749953883107</v>
+        <v>0.01155749953883136</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004801947076014734</v>
+        <v>0.004801947076014758</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01842933587649891</v>
+        <v>0.01842933587649925</v>
       </c>
     </row>
     <row r="13">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.01023934088509111</v>
+        <v>0.01023934088509129</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005373597862283417</v>
+        <v>0.005373597862283406</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01632742892970059</v>
+        <v>0.01632742892970077</v>
       </c>
     </row>
     <row r="14">
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.01017034629079663</v>
+        <v>0.01017034629079686</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003760355901858563</v>
+        <v>0.003760355901858599</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01621741165930022</v>
+        <v>0.01621741165930048</v>
       </c>
     </row>
     <row r="15">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.007556786977392827</v>
+        <v>0.00755678697739306</v>
       </c>
       <c r="H15" t="n">
-        <v>0.003631487163269581</v>
+        <v>0.00363148716326959</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0120498871650927</v>
+        <v>0.012049887165093</v>
       </c>
     </row>
     <row r="16">
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.006568436404767208</v>
+        <v>0.006568436404767441</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002196072363767359</v>
+        <v>0.002196072363767321</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01047388496795225</v>
+        <v>0.01047388496795255</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.00593297067347579</v>
+        <v>0.005932970673476113</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00123612970626391</v>
+        <v>0.001236129706263946</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0094605852173767</v>
+        <v>0.009460585217377153</v>
       </c>
     </row>
     <row r="18">
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.005420439767237373</v>
+        <v>0.005420439767237617</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001535155879387675</v>
+        <v>0.001535155879387661</v>
       </c>
       <c r="I18" t="n">
-        <v>0.008643314648909994</v>
+        <v>0.008643314648910327</v>
       </c>
     </row>
     <row r="19">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.005314336291431809</v>
+        <v>0.005314336291432064</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002030618974674196</v>
+        <v>0.002030618974674223</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008474124368026584</v>
+        <v>0.008474124368026937</v>
       </c>
     </row>
     <row r="20">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.003514350607873695</v>
+        <v>0.003514350607873906</v>
       </c>
       <c r="H20" t="n">
-        <v>0.006110902823824402</v>
+        <v>0.006110902823824397</v>
       </c>
       <c r="I20" t="n">
-        <v>0.005603906582273851</v>
+        <v>0.00560390658227415</v>
       </c>
     </row>
     <row r="21">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.0034441481240021</v>
+        <v>0.003444148124002267</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00237696540288218</v>
+        <v>0.002376965402882182</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005491963237583484</v>
+        <v>0.005491963237583713</v>
       </c>
     </row>
     <row r="22">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.002929585104837673</v>
+        <v>0.002929585104837884</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001094060827094026</v>
+        <v>0.001094060827094021</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004671452306309358</v>
+        <v>0.004671452306309664</v>
       </c>
     </row>
     <row r="23">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.0008430978935825229</v>
+        <v>0.0008430978935827227</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001967829439132348</v>
+        <v>0.001967829439132394</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001344385453393022</v>
+        <v>0.001344385453393331</v>
       </c>
     </row>
     <row r="24">
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.0002509742748877164</v>
+        <v>0.0002509742748878829</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001396474164201583</v>
+        <v>0.001396474164201592</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0004001980872009875</v>
+        <v>0.0004001980872012504</v>
       </c>
     </row>
     <row r="25">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-3.471688116681859e-05</v>
+        <v>-3.471688116660765e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0005124481320309013</v>
+        <v>0.0005124481320309753</v>
       </c>
       <c r="I25" t="n">
-        <v>5.535877907311685e-05</v>
+        <v>5.535877907278012e-05</v>
       </c>
     </row>
     <row r="26">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.0006610909967943335</v>
+        <v>-0.000661090996794167</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002634289943162154</v>
+        <v>0.002634289943162112</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001054161238243447</v>
+        <v>0.001054161238243175</v>
       </c>
     </row>
     <row r="27">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.001380781816066512</v>
+        <v>-0.001380781816066234</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002252328579339999</v>
+        <v>0.002252328579340026</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00220176447119509</v>
+        <v>0.002201764471194633</v>
       </c>
     </row>
     <row r="28">
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.004036032184131799</v>
+        <v>-0.004036032184131589</v>
       </c>
       <c r="H28" t="n">
-        <v>0.003272425233031639</v>
+        <v>0.003272425233031629</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006435768608929348</v>
+        <v>0.006435768608928969</v>
       </c>
     </row>
     <row r="29">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.005908712413299766</v>
+        <v>-0.005908712413299511</v>
       </c>
       <c r="H29" t="n">
-        <v>0.003273920317167908</v>
+        <v>0.003273920317167925</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0094219035264918</v>
+        <v>0.009421903526491332</v>
       </c>
     </row>
   </sheetData>

--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -1753,10 +1753,10 @@
         <v>0.1208222616241151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04624424822799005</v>
+        <v>0.04624424822799</v>
       </c>
       <c r="I2" t="n">
-        <v>0.192660534689862</v>
+        <v>0.1926605346898621</v>
       </c>
     </row>
     <row r="3">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.09493913788330646</v>
+        <v>0.09493913788330641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02091437723053539</v>
+        <v>0.02091437723053537</v>
       </c>
       <c r="I3" t="n">
         <v>0.1513878719179812</v>
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.07244755600675354</v>
+        <v>0.07244755600675355</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01979407399214914</v>
+        <v>0.01979407399214918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1155232875929629</v>
+        <v>0.115523287592963</v>
       </c>
     </row>
     <row r="5">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.05449786362675575</v>
+        <v>0.05449786362675568</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02412711720990969</v>
+        <v>0.02412711720990975</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08690110087866716</v>
+        <v>0.08690110087866711</v>
       </c>
     </row>
     <row r="6">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.0489380260927848</v>
+        <v>0.04893802609278484</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01125272720760455</v>
+        <v>0.01125272720760452</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07803550560106799</v>
+        <v>0.0780355056010681</v>
       </c>
     </row>
     <row r="7">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.04452986308632003</v>
+        <v>0.04452986308632002</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01363313217761005</v>
+        <v>0.01363313217761004</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07100634532539191</v>
+        <v>0.07100634532539195</v>
       </c>
     </row>
     <row r="8">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04104928587923673</v>
+        <v>0.04104928587923672</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007389694768749083</v>
+        <v>0.007389694768749048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06545629306902713</v>
+        <v>0.06545629306902716</v>
       </c>
     </row>
     <row r="9">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.03263091459899287</v>
+        <v>0.03263091459899289</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008536093787784131</v>
+        <v>0.00853609378778414</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0520325424268206</v>
+        <v>0.05203254242682067</v>
       </c>
     </row>
     <row r="10">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.0185968481339127</v>
+        <v>0.01859684813391271</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01117624141826799</v>
+        <v>0.01117624141826803</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0296541271191589</v>
+        <v>0.02965412711915893</v>
       </c>
     </row>
     <row r="11">
@@ -2104,10 +2104,10 @@
         <v>0.01290971951045696</v>
       </c>
       <c r="H11" t="n">
-        <v>0.004259142807845136</v>
+        <v>0.004259142807845178</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0205855562555068</v>
+        <v>0.02058555625550681</v>
       </c>
     </row>
     <row r="12">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.01155749953883136</v>
+        <v>0.01155749953883128</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004801947076014758</v>
+        <v>0.004801947076014736</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01842933587649925</v>
+        <v>0.01842933587649914</v>
       </c>
     </row>
     <row r="13">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.01023934088509129</v>
+        <v>0.01023934088509133</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005373597862283406</v>
+        <v>0.005373597862283404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01632742892970077</v>
+        <v>0.01632742892970085</v>
       </c>
     </row>
     <row r="14">
@@ -2221,10 +2221,10 @@
         <v>0.01017034629079686</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003760355901858599</v>
+        <v>0.00376035590185859</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01621741165930048</v>
+        <v>0.01621741165930049</v>
       </c>
     </row>
     <row r="15">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.00755678697739306</v>
+        <v>0.007556786977392959</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00363148716326959</v>
+        <v>0.003631487163269547</v>
       </c>
       <c r="I15" t="n">
-        <v>0.012049887165093</v>
+        <v>0.01204988716509284</v>
       </c>
     </row>
     <row r="16">
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.006568436404767441</v>
+        <v>0.00656843640476742</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002196072363767321</v>
+        <v>0.002196072363767325</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01047388496795255</v>
+        <v>0.01047388496795252</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.005932970673476113</v>
+        <v>0.005932970673476035</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001236129706263946</v>
+        <v>0.001236129706263939</v>
       </c>
       <c r="I17" t="n">
-        <v>0.009460585217377153</v>
+        <v>0.009460585217377035</v>
       </c>
     </row>
     <row r="18">
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.005420439767237617</v>
+        <v>0.005420439767237595</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001535155879387661</v>
+        <v>0.001535155879387639</v>
       </c>
       <c r="I18" t="n">
-        <v>0.008643314648910327</v>
+        <v>0.008643314648910298</v>
       </c>
     </row>
     <row r="19">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.005314336291432064</v>
+        <v>0.005314336291432043</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002030618974674223</v>
+        <v>0.002030618974674219</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008474124368026937</v>
+        <v>0.008474124368026907</v>
       </c>
     </row>
     <row r="20">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.003514350607873906</v>
+        <v>0.003514350607873895</v>
       </c>
       <c r="H20" t="n">
-        <v>0.006110902823824397</v>
+        <v>0.006110902823824425</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00560390658227415</v>
+        <v>0.005603906582274137</v>
       </c>
     </row>
     <row r="21">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.003444148124002267</v>
+        <v>0.0034441481240023</v>
       </c>
       <c r="H21" t="n">
-        <v>0.002376965402882182</v>
+        <v>0.002376965402882198</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005491963237583713</v>
+        <v>0.00549196323758377</v>
       </c>
     </row>
     <row r="22">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.002929585104837884</v>
+        <v>0.00292958510483784</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001094060827094021</v>
+        <v>0.001094060827094062</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004671452306309664</v>
+        <v>0.004671452306309595</v>
       </c>
     </row>
     <row r="23">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.0008430978935827227</v>
+        <v>0.0008430978935826782</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001967829439132394</v>
+        <v>0.00196782943913237</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001344385453393331</v>
+        <v>0.001344385453393262</v>
       </c>
     </row>
     <row r="24">
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.0002509742748878829</v>
+        <v>0.0002509742748879384</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001396474164201592</v>
+        <v>0.001396474164201551</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0004001980872012504</v>
+        <v>0.0004001980872013393</v>
       </c>
     </row>
     <row r="25">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-3.471688116660765e-05</v>
+        <v>-3.471688116657434e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0005124481320309753</v>
+        <v>0.0005124481320309497</v>
       </c>
       <c r="I25" t="n">
-        <v>5.535877907278012e-05</v>
+        <v>5.535877907272705e-05</v>
       </c>
     </row>
     <row r="26">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.000661090996794167</v>
+        <v>-0.000661090996794067</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002634289943162112</v>
+        <v>0.002634289943162153</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001054161238243175</v>
+        <v>0.001054161238243016</v>
       </c>
     </row>
     <row r="27">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.001380781816066234</v>
+        <v>-0.001380781816066257</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002252328579340026</v>
+        <v>0.002252328579339981</v>
       </c>
       <c r="I27" t="n">
-        <v>0.002201764471194633</v>
+        <v>0.00220176447119467</v>
       </c>
     </row>
     <row r="28">
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.004036032184131589</v>
+        <v>-0.004036032184131577</v>
       </c>
       <c r="H28" t="n">
-        <v>0.003272425233031629</v>
+        <v>0.003272425233031707</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006435768608928969</v>
+        <v>0.006435768608928956</v>
       </c>
     </row>
     <row r="29">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.005908712413299511</v>
+        <v>-0.005908712413299588</v>
       </c>
       <c r="H29" t="n">
-        <v>0.003273920317167925</v>
+        <v>0.00327392031716794</v>
       </c>
       <c r="I29" t="n">
-        <v>0.009421903526491332</v>
+        <v>0.00942190352649146</v>
       </c>
     </row>
   </sheetData>

--- a/NN/reports/model_b_feature_importance_analysis.xlsx
+++ b/NN/reports/model_b_feature_importance_analysis.xlsx
@@ -1753,10 +1753,10 @@
         <v>0.1208222616241151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04624424822799</v>
+        <v>0.04624424822799001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1926605346898621</v>
+        <v>0.1926605346898625</v>
       </c>
     </row>
     <row r="3">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.09493913788330641</v>
+        <v>0.09493913788330627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02091437723053537</v>
+        <v>0.02091437723053539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1513878719179812</v>
+        <v>0.1513878719179814</v>
       </c>
     </row>
     <row r="4">
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.07244755600675355</v>
+        <v>0.0724475560067535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01979407399214918</v>
+        <v>0.01979407399214919</v>
       </c>
       <c r="I4" t="n">
-        <v>0.115523287592963</v>
+        <v>0.1155232875929632</v>
       </c>
     </row>
     <row r="5">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.05449786362675568</v>
+        <v>0.05449786362675563</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02412711720990975</v>
+        <v>0.02412711720990974</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08690110087866711</v>
+        <v>0.08690110087866723</v>
       </c>
     </row>
     <row r="6">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.04893802609278484</v>
+        <v>0.04893802609278469</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01125272720760452</v>
+        <v>0.01125272720760451</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0780355056010681</v>
+        <v>0.07803550560106806</v>
       </c>
     </row>
     <row r="7">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.04452986308632002</v>
+        <v>0.04452986308631986</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01363313217761004</v>
+        <v>0.01363313217761006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07100634532539195</v>
+        <v>0.07100634532539185</v>
       </c>
     </row>
     <row r="8">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.04104928587923672</v>
+        <v>0.04104928587923664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007389694768749048</v>
+        <v>0.007389694768749001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06545629306902716</v>
+        <v>0.0654562930690272</v>
       </c>
     </row>
     <row r="9">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.03263091459899289</v>
+        <v>0.03263091459899274</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00853609378778414</v>
+        <v>0.008536093787784214</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05203254242682067</v>
+        <v>0.05203254242682057</v>
       </c>
     </row>
     <row r="10">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.01859684813391271</v>
+        <v>0.01859684813391261</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01117624141826803</v>
+        <v>0.01117624141826805</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02965412711915893</v>
+        <v>0.02965412711915884</v>
       </c>
     </row>
     <row r="11">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.01290971951045696</v>
+        <v>0.01290971951045687</v>
       </c>
       <c r="H11" t="n">
-        <v>0.004259142807845178</v>
+        <v>0.004259142807845207</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02058555625550681</v>
+        <v>0.02058555625550672</v>
       </c>
     </row>
     <row r="12">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.01155749953883128</v>
+        <v>0.0115574995388312</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004801947076014736</v>
+        <v>0.00480194707601474</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01842933587649914</v>
+        <v>0.01842933587649905</v>
       </c>
     </row>
     <row r="13">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.01023934088509133</v>
+        <v>0.01023934088509121</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005373597862283404</v>
+        <v>0.005373597862283439</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01632742892970085</v>
+        <v>0.01632742892970069</v>
       </c>
     </row>
     <row r="14">
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.01017034629079686</v>
+        <v>0.01017034629079675</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00376035590185859</v>
+        <v>0.003760355901858563</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01621741165930049</v>
+        <v>0.01621741165930035</v>
       </c>
     </row>
     <row r="15">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.007556786977392959</v>
+        <v>0.007556786977392938</v>
       </c>
       <c r="H15" t="n">
-        <v>0.003631487163269547</v>
+        <v>0.003631487163269567</v>
       </c>
       <c r="I15" t="n">
         <v>0.01204988716509284</v>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.00656843640476742</v>
+        <v>0.006568436404767319</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002196072363767325</v>
+        <v>0.002196072363767351</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01047388496795252</v>
+        <v>0.01047388496795239</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.005932970673476035</v>
+        <v>0.005932970673475901</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001236129706263939</v>
+        <v>0.001236129706263926</v>
       </c>
       <c r="I17" t="n">
-        <v>0.009460585217377035</v>
+        <v>0.009460585217376846</v>
       </c>
     </row>
     <row r="18">
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.005420439767237595</v>
+        <v>0.005420439767237495</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001535155879387639</v>
+        <v>0.001535155879387615</v>
       </c>
       <c r="I18" t="n">
-        <v>0.008643314648910298</v>
+        <v>0.008643314648910161</v>
       </c>
     </row>
     <row r="19">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.005314336291432043</v>
+        <v>0.005314336291431932</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002030618974674219</v>
+        <v>0.002030618974674234</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008474124368026907</v>
+        <v>0.008474124368026751</v>
       </c>
     </row>
     <row r="20">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.003514350607873895</v>
+        <v>0.003514350607873773</v>
       </c>
       <c r="H20" t="n">
-        <v>0.006110902823824425</v>
+        <v>0.006110902823824435</v>
       </c>
       <c r="I20" t="n">
-        <v>0.005603906582274137</v>
+        <v>0.005603906582273956</v>
       </c>
     </row>
     <row r="21">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.0034441481240023</v>
+        <v>0.003444148124002233</v>
       </c>
       <c r="H21" t="n">
-        <v>0.002376965402882198</v>
+        <v>0.002376965402882154</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00549196323758377</v>
+        <v>0.005491963237583677</v>
       </c>
     </row>
     <row r="22">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.00292958510483784</v>
+        <v>0.002929585104837751</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001094060827094062</v>
+        <v>0.001094060827094005</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004671452306309595</v>
+        <v>0.004671452306309465</v>
       </c>
     </row>
     <row r="23">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.0008430978935826782</v>
+        <v>0.0008430978935825339</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00196782943913237</v>
+        <v>0.001967829439132374</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001344385453393262</v>
+        <v>0.001344385453393035</v>
       </c>
     </row>
     <row r="24">
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.0002509742748879384</v>
+        <v>0.0002509742748878385</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001396474164201551</v>
+        <v>0.001396474164201579</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0004001980872013393</v>
+        <v>0.0004001980872011809</v>
       </c>
     </row>
     <row r="25">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-3.471688116657434e-05</v>
+        <v>-3.471688116671867e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0005124481320309497</v>
+        <v>0.0005124481320309708</v>
       </c>
       <c r="I25" t="n">
-        <v>5.535877907272705e-05</v>
+        <v>5.535877907295733e-05</v>
       </c>
     </row>
     <row r="26">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0.000661090996794067</v>
+        <v>-0.0006610909967942113</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002634289943162153</v>
+        <v>0.002634289943162097</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001054161238243016</v>
+        <v>0.001054161238243249</v>
       </c>
     </row>
     <row r="27">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0.001380781816066257</v>
+        <v>-0.001380781816066401</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002252328579339981</v>
+        <v>0.002252328579340005</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00220176447119467</v>
+        <v>0.002201764471194905</v>
       </c>
     </row>
     <row r="28">
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0.004036032184131577</v>
+        <v>-0.004036032184131666</v>
       </c>
       <c r="H28" t="n">
-        <v>0.003272425233031707</v>
+        <v>0.003272425233031627</v>
       </c>
       <c r="I28" t="n">
-        <v>0.006435768608928956</v>
+        <v>0.006435768608929113</v>
       </c>
     </row>
     <row r="29">
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0.005908712413299588</v>
+        <v>-0.005908712413299699</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00327392031716794</v>
+        <v>0.003273920317167892</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00942190352649146</v>
+        <v>0.009421903526491662</v>
       </c>
     </row>
   </sheetData>
